--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260608.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.28%</t>
+          <t>12.44%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>10.60%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.03%</t>
+          <t>9.31%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.32%</t>
+          <t>7.40%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.57%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>9,932</t>
+          <t>21,103</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,103</t>
+          <t>9,932</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1012,24 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>53,029</t>
+          <t>18,120</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>18,120</t>
+          <t>53,029</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1078,24 +1078,24 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>34,552</t>
+          <t>14,428</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>14,428</t>
+          <t>34,552</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1518,24 +1518,24 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>77,540</t>
+          <t>18,188</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>18,188</t>
+          <t>77,540</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1584,24 +1584,24 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>75,391</t>
+          <t>8,750</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>8,750</t>
+          <t>75,391</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>138,231,550</t>
+          <t>90,952,312</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
